--- a/convert/data_thang4.xlsx
+++ b/convert/data_thang4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="77">
   <si>
     <t>Công ty TNHH Sản Xuất Hiệp Phước Thành</t>
   </si>
@@ -151,7 +151,7 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>P</t>
+    <t>Co don nhung di lam</t>
   </si>
   <si>
     <t>2022-04-02</t>
@@ -236,9 +236,6 @@
   </si>
   <si>
     <t>2022-04-09</t>
-  </si>
-  <si>
-    <t>L</t>
   </si>
   <si>
     <t>2022-04-10</t>
@@ -1389,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -1403,7 +1400,7 @@
         <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>51</v>
@@ -1468,7 +1465,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1545,7 +1542,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
